--- a/resources/variable_schema_data_individual_health_template.xlsx
+++ b/resources/variable_schema_data_individual_health_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B1253D-3194-48D9-9DBF-69C638B3D898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCCB87E-4ECA-4116-8409-2764BAE590B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="386">
   <si>
     <t>rule_type</t>
   </si>
@@ -941,6 +941,243 @@
   </si>
   <si>
     <t>المنطقة الإدارية 4</t>
+  </si>
+  <si>
+    <t>age_cat</t>
+  </si>
+  <si>
+    <t>0-4y</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>0-4y,0-4</t>
+  </si>
+  <si>
+    <t>Age Category</t>
+  </si>
+  <si>
+    <t>Catégorie d'âge</t>
+  </si>
+  <si>
+    <t>فئة العمر</t>
+  </si>
+  <si>
+    <t>5-9y</t>
+  </si>
+  <si>
+    <t>5-9y,5-9</t>
+  </si>
+  <si>
+    <t>10-14y</t>
+  </si>
+  <si>
+    <t>10-14y,10-14</t>
+  </si>
+  <si>
+    <t>15-19y</t>
+  </si>
+  <si>
+    <t>15-19y,15-19</t>
+  </si>
+  <si>
+    <t>20-24y</t>
+  </si>
+  <si>
+    <t>20-24y,20-24</t>
+  </si>
+  <si>
+    <t>25-29y</t>
+  </si>
+  <si>
+    <t>25-29y,25-29</t>
+  </si>
+  <si>
+    <t>30-34y</t>
+  </si>
+  <si>
+    <t>30-34y,30-34</t>
+  </si>
+  <si>
+    <t>35-39y</t>
+  </si>
+  <si>
+    <t>35-39y,35-39</t>
+  </si>
+  <si>
+    <t>40-44y</t>
+  </si>
+  <si>
+    <t>40-44y,40-44</t>
+  </si>
+  <si>
+    <t>45-49y</t>
+  </si>
+  <si>
+    <t>45-49y,45-49</t>
+  </si>
+  <si>
+    <t>50-54y</t>
+  </si>
+  <si>
+    <t>50-54y,50-54</t>
+  </si>
+  <si>
+    <t>55-59y</t>
+  </si>
+  <si>
+    <t>55-59y,55-59</t>
+  </si>
+  <si>
+    <t>60-64y</t>
+  </si>
+  <si>
+    <t>60-64y,60-64</t>
+  </si>
+  <si>
+    <t>65-69y</t>
+  </si>
+  <si>
+    <t>65-69y,65-69</t>
+  </si>
+  <si>
+    <t>70-74y</t>
+  </si>
+  <si>
+    <t>70-74y,70-74</t>
+  </si>
+  <si>
+    <t>75-79y</t>
+  </si>
+  <si>
+    <t>75-79y,75-79</t>
+  </si>
+  <si>
+    <t>80-84y</t>
+  </si>
+  <si>
+    <t>80-84y,80-84</t>
+  </si>
+  <si>
+    <t>85-89y</t>
+  </si>
+  <si>
+    <t>85-89y,85-89</t>
+  </si>
+  <si>
+    <t>90-94y</t>
+  </si>
+  <si>
+    <t>90-94y,90-94</t>
+  </si>
+  <si>
+    <t>95-99y</t>
+  </si>
+  <si>
+    <t>95-99y,95-99</t>
+  </si>
+  <si>
+    <t>100-104y</t>
+  </si>
+  <si>
+    <t>100-104y,100-104</t>
+  </si>
+  <si>
+    <t>105-109y</t>
+  </si>
+  <si>
+    <t>105-109y,105-109</t>
+  </si>
+  <si>
+    <t>110-114y</t>
+  </si>
+  <si>
+    <t>110-114y,110-114</t>
+  </si>
+  <si>
+    <t>115-119y</t>
+  </si>
+  <si>
+    <t>115-119y,115-119</t>
+  </si>
+  <si>
+    <t>120-124y</t>
+  </si>
+  <si>
+    <t>120-124y,120-124</t>
+  </si>
+  <si>
+    <t>age_months_cat</t>
+  </si>
+  <si>
+    <t>0-5m</t>
+  </si>
+  <si>
+    <t>0-5m,0-5</t>
+  </si>
+  <si>
+    <t>Age Category (Months)</t>
+  </si>
+  <si>
+    <t>Catégorie d'âge (mois)</t>
+  </si>
+  <si>
+    <t>فئة العمر (بالأشهر)</t>
+  </si>
+  <si>
+    <t>6-11m</t>
+  </si>
+  <si>
+    <t>6-11m,6-11</t>
+  </si>
+  <si>
+    <t>12-17m</t>
+  </si>
+  <si>
+    <t>12-17m,12-17</t>
+  </si>
+  <si>
+    <t>18-23m</t>
+  </si>
+  <si>
+    <t>18-23m,18-23</t>
+  </si>
+  <si>
+    <t>24-29m</t>
+  </si>
+  <si>
+    <t>24-29m,24-29</t>
+  </si>
+  <si>
+    <t>30-35m</t>
+  </si>
+  <si>
+    <t>30-35m,30-35</t>
+  </si>
+  <si>
+    <t>36-41m</t>
+  </si>
+  <si>
+    <t>36-41m,36-41</t>
+  </si>
+  <si>
+    <t>42-47m</t>
+  </si>
+  <si>
+    <t>42-47m,42-47</t>
+  </si>
+  <si>
+    <t>48-53m</t>
+  </si>
+  <si>
+    <t>48-53m,48-53</t>
+  </si>
+  <si>
+    <t>54-59m</t>
+  </si>
+  <si>
+    <t>54-59m,54-59</t>
   </si>
 </sst>
 </file>
@@ -982,7 +1219,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1631,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
@@ -4891,108 +5148,1549 @@
         <v>74</v>
       </c>
     </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" t="s">
+        <v>307</v>
+      </c>
+      <c r="C86" t="s">
+        <v>308</v>
+      </c>
+      <c r="E86" t="s">
+        <v>309</v>
+      </c>
+      <c r="F86" t="s">
+        <v>262</v>
+      </c>
+      <c r="I86" t="s">
+        <v>310</v>
+      </c>
+      <c r="J86" t="s">
+        <v>307</v>
+      </c>
+      <c r="L86" t="s">
+        <v>311</v>
+      </c>
+      <c r="M86" t="s">
+        <v>312</v>
+      </c>
+      <c r="N86" t="s">
+        <v>313</v>
+      </c>
+      <c r="O86" t="s">
+        <v>308</v>
+      </c>
+      <c r="P86" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>307</v>
+      </c>
+      <c r="C87" t="s">
+        <v>314</v>
+      </c>
+      <c r="E87" t="s">
+        <v>309</v>
+      </c>
+      <c r="F87" t="s">
+        <v>262</v>
+      </c>
+      <c r="I87" t="s">
+        <v>315</v>
+      </c>
+      <c r="J87" t="s">
+        <v>307</v>
+      </c>
+      <c r="L87" t="s">
+        <v>311</v>
+      </c>
+      <c r="M87" t="s">
+        <v>312</v>
+      </c>
+      <c r="N87" t="s">
+        <v>313</v>
+      </c>
+      <c r="O87" t="s">
+        <v>314</v>
+      </c>
+      <c r="P87" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>307</v>
+      </c>
+      <c r="C88" t="s">
+        <v>316</v>
+      </c>
+      <c r="E88" t="s">
+        <v>309</v>
+      </c>
+      <c r="F88" t="s">
+        <v>262</v>
+      </c>
+      <c r="I88" t="s">
+        <v>317</v>
+      </c>
+      <c r="J88" t="s">
+        <v>307</v>
+      </c>
+      <c r="L88" t="s">
+        <v>311</v>
+      </c>
+      <c r="M88" t="s">
+        <v>312</v>
+      </c>
+      <c r="N88" t="s">
+        <v>313</v>
+      </c>
+      <c r="O88" t="s">
+        <v>316</v>
+      </c>
+      <c r="P88" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B89" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" t="s">
+        <v>318</v>
+      </c>
+      <c r="E89" t="s">
+        <v>309</v>
+      </c>
+      <c r="F89" t="s">
+        <v>262</v>
+      </c>
+      <c r="I89" t="s">
+        <v>319</v>
+      </c>
+      <c r="J89" t="s">
+        <v>307</v>
+      </c>
+      <c r="L89" t="s">
+        <v>311</v>
+      </c>
+      <c r="M89" t="s">
+        <v>312</v>
+      </c>
+      <c r="N89" t="s">
+        <v>313</v>
+      </c>
+      <c r="O89" t="s">
+        <v>318</v>
+      </c>
+      <c r="P89" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>307</v>
+      </c>
+      <c r="C90" t="s">
+        <v>320</v>
+      </c>
+      <c r="E90" t="s">
+        <v>309</v>
+      </c>
+      <c r="F90" t="s">
+        <v>262</v>
+      </c>
+      <c r="I90" t="s">
+        <v>321</v>
+      </c>
+      <c r="J90" t="s">
+        <v>307</v>
+      </c>
+      <c r="L90" t="s">
+        <v>311</v>
+      </c>
+      <c r="M90" t="s">
+        <v>312</v>
+      </c>
+      <c r="N90" t="s">
+        <v>313</v>
+      </c>
+      <c r="O90" t="s">
+        <v>320</v>
+      </c>
+      <c r="P90" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>307</v>
+      </c>
+      <c r="C91" t="s">
+        <v>322</v>
+      </c>
+      <c r="E91" t="s">
+        <v>309</v>
+      </c>
+      <c r="F91" t="s">
+        <v>262</v>
+      </c>
+      <c r="I91" t="s">
+        <v>323</v>
+      </c>
+      <c r="J91" t="s">
+        <v>307</v>
+      </c>
+      <c r="L91" t="s">
+        <v>311</v>
+      </c>
+      <c r="M91" t="s">
+        <v>312</v>
+      </c>
+      <c r="N91" t="s">
+        <v>313</v>
+      </c>
+      <c r="O91" t="s">
+        <v>322</v>
+      </c>
+      <c r="P91" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>307</v>
+      </c>
+      <c r="C92" t="s">
+        <v>324</v>
+      </c>
+      <c r="E92" t="s">
+        <v>309</v>
+      </c>
+      <c r="F92" t="s">
+        <v>262</v>
+      </c>
+      <c r="I92" t="s">
+        <v>325</v>
+      </c>
+      <c r="J92" t="s">
+        <v>307</v>
+      </c>
+      <c r="L92" t="s">
+        <v>311</v>
+      </c>
+      <c r="M92" t="s">
+        <v>312</v>
+      </c>
+      <c r="N92" t="s">
+        <v>313</v>
+      </c>
+      <c r="O92" t="s">
+        <v>324</v>
+      </c>
+      <c r="P92" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>307</v>
+      </c>
+      <c r="C93" t="s">
+        <v>326</v>
+      </c>
+      <c r="E93" t="s">
+        <v>309</v>
+      </c>
+      <c r="F93" t="s">
+        <v>262</v>
+      </c>
+      <c r="I93" t="s">
+        <v>327</v>
+      </c>
+      <c r="J93" t="s">
+        <v>307</v>
+      </c>
+      <c r="L93" t="s">
+        <v>311</v>
+      </c>
+      <c r="M93" t="s">
+        <v>312</v>
+      </c>
+      <c r="N93" t="s">
+        <v>313</v>
+      </c>
+      <c r="O93" t="s">
+        <v>326</v>
+      </c>
+      <c r="P93" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1</v>
+      </c>
+      <c r="B94" t="s">
+        <v>307</v>
+      </c>
+      <c r="C94" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" t="s">
+        <v>309</v>
+      </c>
+      <c r="F94" t="s">
+        <v>262</v>
+      </c>
+      <c r="I94" t="s">
+        <v>329</v>
+      </c>
+      <c r="J94" t="s">
+        <v>307</v>
+      </c>
+      <c r="L94" t="s">
+        <v>311</v>
+      </c>
+      <c r="M94" t="s">
+        <v>312</v>
+      </c>
+      <c r="N94" t="s">
+        <v>313</v>
+      </c>
+      <c r="O94" t="s">
+        <v>328</v>
+      </c>
+      <c r="P94" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>307</v>
+      </c>
+      <c r="C95" t="s">
+        <v>330</v>
+      </c>
+      <c r="E95" t="s">
+        <v>309</v>
+      </c>
+      <c r="F95" t="s">
+        <v>262</v>
+      </c>
+      <c r="I95" t="s">
+        <v>331</v>
+      </c>
+      <c r="J95" t="s">
+        <v>307</v>
+      </c>
+      <c r="L95" t="s">
+        <v>311</v>
+      </c>
+      <c r="M95" t="s">
+        <v>312</v>
+      </c>
+      <c r="N95" t="s">
+        <v>313</v>
+      </c>
+      <c r="O95" t="s">
+        <v>330</v>
+      </c>
+      <c r="P95" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1</v>
+      </c>
+      <c r="B96" t="s">
+        <v>307</v>
+      </c>
+      <c r="C96" t="s">
+        <v>332</v>
+      </c>
+      <c r="E96" t="s">
+        <v>309</v>
+      </c>
+      <c r="F96" t="s">
+        <v>262</v>
+      </c>
+      <c r="I96" t="s">
+        <v>333</v>
+      </c>
+      <c r="J96" t="s">
+        <v>307</v>
+      </c>
+      <c r="L96" t="s">
+        <v>311</v>
+      </c>
+      <c r="M96" t="s">
+        <v>312</v>
+      </c>
+      <c r="N96" t="s">
+        <v>313</v>
+      </c>
+      <c r="O96" t="s">
+        <v>332</v>
+      </c>
+      <c r="P96" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1</v>
+      </c>
+      <c r="B97" t="s">
+        <v>307</v>
+      </c>
+      <c r="C97" t="s">
+        <v>334</v>
+      </c>
+      <c r="E97" t="s">
+        <v>309</v>
+      </c>
+      <c r="F97" t="s">
+        <v>262</v>
+      </c>
+      <c r="I97" t="s">
+        <v>335</v>
+      </c>
+      <c r="J97" t="s">
+        <v>307</v>
+      </c>
+      <c r="L97" t="s">
+        <v>311</v>
+      </c>
+      <c r="M97" t="s">
+        <v>312</v>
+      </c>
+      <c r="N97" t="s">
+        <v>313</v>
+      </c>
+      <c r="O97" t="s">
+        <v>334</v>
+      </c>
+      <c r="P97" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98" t="s">
+        <v>307</v>
+      </c>
+      <c r="C98" t="s">
+        <v>336</v>
+      </c>
+      <c r="E98" t="s">
+        <v>309</v>
+      </c>
+      <c r="F98" t="s">
+        <v>262</v>
+      </c>
+      <c r="I98" t="s">
+        <v>337</v>
+      </c>
+      <c r="J98" t="s">
+        <v>307</v>
+      </c>
+      <c r="L98" t="s">
+        <v>311</v>
+      </c>
+      <c r="M98" t="s">
+        <v>312</v>
+      </c>
+      <c r="N98" t="s">
+        <v>313</v>
+      </c>
+      <c r="O98" t="s">
+        <v>336</v>
+      </c>
+      <c r="P98" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="E99" t="s">
+        <v>309</v>
+      </c>
+      <c r="F99" t="s">
+        <v>262</v>
+      </c>
+      <c r="I99" t="s">
+        <v>339</v>
+      </c>
+      <c r="J99" t="s">
+        <v>307</v>
+      </c>
+      <c r="L99" t="s">
+        <v>311</v>
+      </c>
+      <c r="M99" t="s">
+        <v>312</v>
+      </c>
+      <c r="N99" t="s">
+        <v>313</v>
+      </c>
+      <c r="O99" t="s">
+        <v>338</v>
+      </c>
+      <c r="P99" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1</v>
+      </c>
+      <c r="B100" t="s">
+        <v>307</v>
+      </c>
+      <c r="C100" t="s">
+        <v>340</v>
+      </c>
+      <c r="E100" t="s">
+        <v>309</v>
+      </c>
+      <c r="F100" t="s">
+        <v>262</v>
+      </c>
+      <c r="I100" t="s">
+        <v>341</v>
+      </c>
+      <c r="J100" t="s">
+        <v>307</v>
+      </c>
+      <c r="L100" t="s">
+        <v>311</v>
+      </c>
+      <c r="M100" t="s">
+        <v>312</v>
+      </c>
+      <c r="N100" t="s">
+        <v>313</v>
+      </c>
+      <c r="O100" t="s">
+        <v>340</v>
+      </c>
+      <c r="P100" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>307</v>
+      </c>
+      <c r="C101" t="s">
+        <v>342</v>
+      </c>
+      <c r="E101" t="s">
+        <v>309</v>
+      </c>
+      <c r="F101" t="s">
+        <v>262</v>
+      </c>
+      <c r="I101" t="s">
+        <v>343</v>
+      </c>
+      <c r="J101" t="s">
+        <v>307</v>
+      </c>
+      <c r="L101" t="s">
+        <v>311</v>
+      </c>
+      <c r="M101" t="s">
+        <v>312</v>
+      </c>
+      <c r="N101" t="s">
+        <v>313</v>
+      </c>
+      <c r="O101" t="s">
+        <v>342</v>
+      </c>
+      <c r="P101" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" t="s">
+        <v>344</v>
+      </c>
+      <c r="E102" t="s">
+        <v>309</v>
+      </c>
+      <c r="F102" t="s">
+        <v>262</v>
+      </c>
+      <c r="I102" t="s">
+        <v>345</v>
+      </c>
+      <c r="J102" t="s">
+        <v>307</v>
+      </c>
+      <c r="L102" t="s">
+        <v>311</v>
+      </c>
+      <c r="M102" t="s">
+        <v>312</v>
+      </c>
+      <c r="N102" t="s">
+        <v>313</v>
+      </c>
+      <c r="O102" t="s">
+        <v>344</v>
+      </c>
+      <c r="P102" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" t="s">
+        <v>307</v>
+      </c>
+      <c r="C103" t="s">
+        <v>346</v>
+      </c>
+      <c r="E103" t="s">
+        <v>309</v>
+      </c>
+      <c r="F103" t="s">
+        <v>262</v>
+      </c>
+      <c r="I103" t="s">
+        <v>347</v>
+      </c>
+      <c r="J103" t="s">
+        <v>307</v>
+      </c>
+      <c r="L103" t="s">
+        <v>311</v>
+      </c>
+      <c r="M103" t="s">
+        <v>312</v>
+      </c>
+      <c r="N103" t="s">
+        <v>313</v>
+      </c>
+      <c r="O103" t="s">
+        <v>346</v>
+      </c>
+      <c r="P103" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>307</v>
+      </c>
+      <c r="C104" t="s">
+        <v>348</v>
+      </c>
+      <c r="E104" t="s">
+        <v>309</v>
+      </c>
+      <c r="F104" t="s">
+        <v>262</v>
+      </c>
+      <c r="I104" t="s">
+        <v>349</v>
+      </c>
+      <c r="J104" t="s">
+        <v>307</v>
+      </c>
+      <c r="L104" t="s">
+        <v>311</v>
+      </c>
+      <c r="M104" t="s">
+        <v>312</v>
+      </c>
+      <c r="N104" t="s">
+        <v>313</v>
+      </c>
+      <c r="O104" t="s">
+        <v>348</v>
+      </c>
+      <c r="P104" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>307</v>
+      </c>
+      <c r="C105" t="s">
+        <v>350</v>
+      </c>
+      <c r="E105" t="s">
+        <v>309</v>
+      </c>
+      <c r="F105" t="s">
+        <v>262</v>
+      </c>
+      <c r="I105" t="s">
+        <v>351</v>
+      </c>
+      <c r="J105" t="s">
+        <v>307</v>
+      </c>
+      <c r="L105" t="s">
+        <v>311</v>
+      </c>
+      <c r="M105" t="s">
+        <v>312</v>
+      </c>
+      <c r="N105" t="s">
+        <v>313</v>
+      </c>
+      <c r="O105" t="s">
+        <v>350</v>
+      </c>
+      <c r="P105" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>307</v>
+      </c>
+      <c r="C106" t="s">
+        <v>352</v>
+      </c>
+      <c r="E106" t="s">
+        <v>309</v>
+      </c>
+      <c r="F106" t="s">
+        <v>262</v>
+      </c>
+      <c r="I106" t="s">
+        <v>353</v>
+      </c>
+      <c r="J106" t="s">
+        <v>307</v>
+      </c>
+      <c r="L106" t="s">
+        <v>311</v>
+      </c>
+      <c r="M106" t="s">
+        <v>312</v>
+      </c>
+      <c r="N106" t="s">
+        <v>313</v>
+      </c>
+      <c r="O106" t="s">
+        <v>352</v>
+      </c>
+      <c r="P106" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1</v>
+      </c>
+      <c r="B107" t="s">
+        <v>307</v>
+      </c>
+      <c r="C107" t="s">
+        <v>354</v>
+      </c>
+      <c r="E107" t="s">
+        <v>309</v>
+      </c>
+      <c r="F107" t="s">
+        <v>262</v>
+      </c>
+      <c r="I107" t="s">
+        <v>355</v>
+      </c>
+      <c r="J107" t="s">
+        <v>307</v>
+      </c>
+      <c r="L107" t="s">
+        <v>311</v>
+      </c>
+      <c r="M107" t="s">
+        <v>312</v>
+      </c>
+      <c r="N107" t="s">
+        <v>313</v>
+      </c>
+      <c r="O107" t="s">
+        <v>354</v>
+      </c>
+      <c r="P107" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>307</v>
+      </c>
+      <c r="C108" t="s">
+        <v>356</v>
+      </c>
+      <c r="E108" t="s">
+        <v>309</v>
+      </c>
+      <c r="F108" t="s">
+        <v>262</v>
+      </c>
+      <c r="I108" t="s">
+        <v>357</v>
+      </c>
+      <c r="J108" t="s">
+        <v>307</v>
+      </c>
+      <c r="L108" t="s">
+        <v>311</v>
+      </c>
+      <c r="M108" t="s">
+        <v>312</v>
+      </c>
+      <c r="N108" t="s">
+        <v>313</v>
+      </c>
+      <c r="O108" t="s">
+        <v>356</v>
+      </c>
+      <c r="P108" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B109" t="s">
+        <v>307</v>
+      </c>
+      <c r="C109" t="s">
+        <v>358</v>
+      </c>
+      <c r="E109" t="s">
+        <v>309</v>
+      </c>
+      <c r="F109" t="s">
+        <v>262</v>
+      </c>
+      <c r="I109" t="s">
+        <v>359</v>
+      </c>
+      <c r="J109" t="s">
+        <v>307</v>
+      </c>
+      <c r="L109" t="s">
+        <v>311</v>
+      </c>
+      <c r="M109" t="s">
+        <v>312</v>
+      </c>
+      <c r="N109" t="s">
+        <v>313</v>
+      </c>
+      <c r="O109" t="s">
+        <v>358</v>
+      </c>
+      <c r="P109" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>307</v>
+      </c>
+      <c r="C110" t="s">
+        <v>360</v>
+      </c>
+      <c r="E110" t="s">
+        <v>309</v>
+      </c>
+      <c r="F110" t="s">
+        <v>262</v>
+      </c>
+      <c r="I110" t="s">
+        <v>361</v>
+      </c>
+      <c r="J110" t="s">
+        <v>307</v>
+      </c>
+      <c r="L110" t="s">
+        <v>311</v>
+      </c>
+      <c r="M110" t="s">
+        <v>312</v>
+      </c>
+      <c r="N110" t="s">
+        <v>313</v>
+      </c>
+      <c r="O110" t="s">
+        <v>360</v>
+      </c>
+      <c r="P110" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>362</v>
+      </c>
+      <c r="C111" t="s">
+        <v>363</v>
+      </c>
+      <c r="E111" t="s">
+        <v>309</v>
+      </c>
+      <c r="F111" t="s">
+        <v>262</v>
+      </c>
+      <c r="I111" t="s">
+        <v>364</v>
+      </c>
+      <c r="J111" t="s">
+        <v>362</v>
+      </c>
+      <c r="L111" t="s">
+        <v>365</v>
+      </c>
+      <c r="M111" t="s">
+        <v>366</v>
+      </c>
+      <c r="N111" t="s">
+        <v>367</v>
+      </c>
+      <c r="O111" t="s">
+        <v>363</v>
+      </c>
+      <c r="P111" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>362</v>
+      </c>
+      <c r="C112" t="s">
+        <v>368</v>
+      </c>
+      <c r="E112" t="s">
+        <v>309</v>
+      </c>
+      <c r="F112" t="s">
+        <v>262</v>
+      </c>
+      <c r="I112" t="s">
+        <v>369</v>
+      </c>
+      <c r="J112" t="s">
+        <v>362</v>
+      </c>
+      <c r="L112" t="s">
+        <v>365</v>
+      </c>
+      <c r="M112" t="s">
+        <v>366</v>
+      </c>
+      <c r="N112" t="s">
+        <v>367</v>
+      </c>
+      <c r="O112" t="s">
+        <v>368</v>
+      </c>
+      <c r="P112" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>362</v>
+      </c>
+      <c r="C113" t="s">
+        <v>370</v>
+      </c>
+      <c r="E113" t="s">
+        <v>309</v>
+      </c>
+      <c r="F113" t="s">
+        <v>262</v>
+      </c>
+      <c r="I113" t="s">
+        <v>371</v>
+      </c>
+      <c r="J113" t="s">
+        <v>362</v>
+      </c>
+      <c r="L113" t="s">
+        <v>365</v>
+      </c>
+      <c r="M113" t="s">
+        <v>366</v>
+      </c>
+      <c r="N113" t="s">
+        <v>367</v>
+      </c>
+      <c r="O113" t="s">
+        <v>370</v>
+      </c>
+      <c r="P113" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>362</v>
+      </c>
+      <c r="C114" t="s">
+        <v>372</v>
+      </c>
+      <c r="E114" t="s">
+        <v>309</v>
+      </c>
+      <c r="F114" t="s">
+        <v>262</v>
+      </c>
+      <c r="I114" t="s">
+        <v>373</v>
+      </c>
+      <c r="J114" t="s">
+        <v>362</v>
+      </c>
+      <c r="L114" t="s">
+        <v>365</v>
+      </c>
+      <c r="M114" t="s">
+        <v>366</v>
+      </c>
+      <c r="N114" t="s">
+        <v>367</v>
+      </c>
+      <c r="O114" t="s">
+        <v>372</v>
+      </c>
+      <c r="P114" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>362</v>
+      </c>
+      <c r="C115" t="s">
+        <v>374</v>
+      </c>
+      <c r="E115" t="s">
+        <v>309</v>
+      </c>
+      <c r="F115" t="s">
+        <v>262</v>
+      </c>
+      <c r="I115" t="s">
+        <v>375</v>
+      </c>
+      <c r="J115" t="s">
+        <v>362</v>
+      </c>
+      <c r="L115" t="s">
+        <v>365</v>
+      </c>
+      <c r="M115" t="s">
+        <v>366</v>
+      </c>
+      <c r="N115" t="s">
+        <v>367</v>
+      </c>
+      <c r="O115" t="s">
+        <v>374</v>
+      </c>
+      <c r="P115" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>362</v>
+      </c>
+      <c r="C116" t="s">
+        <v>376</v>
+      </c>
+      <c r="E116" t="s">
+        <v>309</v>
+      </c>
+      <c r="F116" t="s">
+        <v>262</v>
+      </c>
+      <c r="I116" t="s">
+        <v>377</v>
+      </c>
+      <c r="J116" t="s">
+        <v>362</v>
+      </c>
+      <c r="L116" t="s">
+        <v>365</v>
+      </c>
+      <c r="M116" t="s">
+        <v>366</v>
+      </c>
+      <c r="N116" t="s">
+        <v>367</v>
+      </c>
+      <c r="O116" t="s">
+        <v>376</v>
+      </c>
+      <c r="P116" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>362</v>
+      </c>
+      <c r="C117" t="s">
+        <v>378</v>
+      </c>
+      <c r="E117" t="s">
+        <v>309</v>
+      </c>
+      <c r="F117" t="s">
+        <v>262</v>
+      </c>
+      <c r="I117" t="s">
+        <v>379</v>
+      </c>
+      <c r="J117" t="s">
+        <v>362</v>
+      </c>
+      <c r="L117" t="s">
+        <v>365</v>
+      </c>
+      <c r="M117" t="s">
+        <v>366</v>
+      </c>
+      <c r="N117" t="s">
+        <v>367</v>
+      </c>
+      <c r="O117" t="s">
+        <v>378</v>
+      </c>
+      <c r="P117" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>362</v>
+      </c>
+      <c r="C118" t="s">
+        <v>380</v>
+      </c>
+      <c r="E118" t="s">
+        <v>309</v>
+      </c>
+      <c r="F118" t="s">
+        <v>262</v>
+      </c>
+      <c r="I118" t="s">
+        <v>381</v>
+      </c>
+      <c r="J118" t="s">
+        <v>362</v>
+      </c>
+      <c r="L118" t="s">
+        <v>365</v>
+      </c>
+      <c r="M118" t="s">
+        <v>366</v>
+      </c>
+      <c r="N118" t="s">
+        <v>367</v>
+      </c>
+      <c r="O118" t="s">
+        <v>380</v>
+      </c>
+      <c r="P118" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>362</v>
+      </c>
+      <c r="C119" t="s">
+        <v>382</v>
+      </c>
+      <c r="E119" t="s">
+        <v>309</v>
+      </c>
+      <c r="F119" t="s">
+        <v>262</v>
+      </c>
+      <c r="I119" t="s">
+        <v>383</v>
+      </c>
+      <c r="J119" t="s">
+        <v>362</v>
+      </c>
+      <c r="L119" t="s">
+        <v>365</v>
+      </c>
+      <c r="M119" t="s">
+        <v>366</v>
+      </c>
+      <c r="N119" t="s">
+        <v>367</v>
+      </c>
+      <c r="O119" t="s">
+        <v>382</v>
+      </c>
+      <c r="P119" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>362</v>
+      </c>
+      <c r="C120" t="s">
+        <v>384</v>
+      </c>
+      <c r="E120" t="s">
+        <v>309</v>
+      </c>
+      <c r="F120" t="s">
+        <v>262</v>
+      </c>
+      <c r="I120" t="s">
+        <v>385</v>
+      </c>
+      <c r="J120" t="s">
+        <v>362</v>
+      </c>
+      <c r="L120" t="s">
+        <v>365</v>
+      </c>
+      <c r="M120" t="s">
+        <v>366</v>
+      </c>
+      <c r="N120" t="s">
+        <v>367</v>
+      </c>
+      <c r="O120" t="s">
+        <v>384</v>
+      </c>
+      <c r="P120" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>384</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B24:B56 B61:B69 B75:B78">
-    <cfRule type="duplicateValues" dxfId="34" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:B59">
-    <cfRule type="duplicateValues" dxfId="33" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:B73">
-    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="31" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79:B85">
-    <cfRule type="duplicateValues" dxfId="30" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:C37">
-    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42:C53 C55">
-    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C71 C73">
-    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75:C78">
-    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79:C82">
-    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H56 H60:H69">
-    <cfRule type="duplicateValues" dxfId="21" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H74">
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27:I35 I37">
-    <cfRule type="duplicateValues" dxfId="19" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42:I53">
-    <cfRule type="duplicateValues" dxfId="18" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I55">
-    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I60:I71">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75:I77">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I79:I81">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J26">
-    <cfRule type="duplicateValues" dxfId="12" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J37">
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J39">
-    <cfRule type="duplicateValues" dxfId="10" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40">
-    <cfRule type="duplicateValues" dxfId="9" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41">
-    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J42:J55">
-    <cfRule type="duplicateValues" dxfId="7" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J57:J59">
-    <cfRule type="duplicateValues" dxfId="6" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J60:J73">
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J74">
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J75:J78">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79:J82">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83:J85">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C86 C88">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I86 I88">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
